--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T08:56:12+00:00</t>
+    <t>2026-03-06T09:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -400,14 +400,24 @@
     <t>Boîte(s) aux lettres du service de messagerie sécurisée de santé (MSS) rattachée(s) à la situation d'exercice.</t>
   </si>
   <si>
-    <t>SituationExercice.exerciceProfessionnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/mos/StructureDefinition/ExerciceProfessionnel)
+    <t>SituationExercice.ExerciceProfessionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/ExerciceProfessionnel
 </t>
   </si>
   <si>
-    <t>Lien vers la classe ExerciceProfessionnel.</t>
+    <t>Lien vers la classe ExerciceProfessionnel</t>
+  </si>
+  <si>
+    <t>SituationExercice.EntiteGeographique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/mos/StructureDefinition/EntiteGeographique
+</t>
+  </si>
+  <si>
+    <t>Lien vers la classe EntiteGeographique</t>
   </si>
 </sst>
 </file>
@@ -709,7 +719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.32421875" customWidth="true" bestFit="true"/>
@@ -722,7 +732,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="63.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2639,6 +2649,106 @@
         <v>71</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T09:16:42+00:00</t>
+    <t>2026-04-20T07:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:14:21+00:00</t>
+    <t>2026-04-20T13:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:39:43+00:00</t>
+    <t>2026-04-20T13:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:49:18+00:00</t>
+    <t>2026-04-20T13:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T13:52:11+00:00</t>
+    <t>2026-04-20T14:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:01:02+00:00</t>
+    <t>2026-04-20T14:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:11:31+00:00</t>
+    <t>2026-04-20T14:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-SituationExercice.xlsx
+++ b/main/ig/StructureDefinition-SituationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T14:36:06+00:00</t>
+    <t>2026-04-20T14:56:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
